--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][CI]Aggregated_U_test.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][CI]Aggregated_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_P2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_P1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SD_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Median_P1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Median_P2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Median_difference_P2_minus_P1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -495,40 +507,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1740</v>
+        <v>1680</v>
       </c>
       <c r="C2" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="D2" t="n">
-        <v>10.69594715118296</v>
+        <v>10.67141302606241</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2657999175524</v>
+        <v>12.28697480121733</v>
       </c>
       <c r="F2" t="n">
-        <v>4.549335527587496</v>
+        <v>4.473128511671421</v>
       </c>
       <c r="G2" t="n">
-        <v>3.130484395771349</v>
+        <v>3.181545380987908</v>
       </c>
       <c r="H2" t="n">
-        <v>10.7314873644225</v>
+        <v>10.74070716503705</v>
       </c>
       <c r="I2" t="n">
-        <v>11.93375641291675</v>
+        <v>11.94403888975615</v>
       </c>
       <c r="J2" t="n">
-        <v>1.202269048494252</v>
+        <v>1.203331724719101</v>
       </c>
       <c r="K2" t="n">
-        <v>290789</v>
+        <v>318979</v>
       </c>
       <c r="L2" t="n">
-        <v>7.834141429356811e-11</v>
+        <v>2.771461151270562e-12</v>
       </c>
       <c r="M2" t="n">
-        <v>3.133656571742724e-10</v>
+        <v>1.108584460508225e-11</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -541,40 +553,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1740</v>
+        <v>1680</v>
       </c>
       <c r="C3" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="D3" t="n">
-        <v>70.25361403517788</v>
+        <v>70.37873783605816</v>
       </c>
       <c r="E3" t="n">
-        <v>79.21656416527743</v>
+        <v>79.21665074189313</v>
       </c>
       <c r="F3" t="n">
-        <v>11.2008835174575</v>
+        <v>11.22723709548191</v>
       </c>
       <c r="G3" t="n">
-        <v>8.270312187988115</v>
+        <v>8.342653957805618</v>
       </c>
       <c r="H3" t="n">
-        <v>70.18243977926325</v>
+        <v>70.29287677939081</v>
       </c>
       <c r="I3" t="n">
-        <v>79.73920634977685</v>
+        <v>79.76082855786311</v>
       </c>
       <c r="J3" t="n">
-        <v>9.556766570513602</v>
+        <v>9.467951778472298</v>
       </c>
       <c r="K3" t="n">
-        <v>191727</v>
+        <v>215183</v>
       </c>
       <c r="L3" t="n">
-        <v>8.966796451384866e-52</v>
+        <v>7.040331823853164e-55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.586718580553946e-51</v>
+        <v>2.816132729541266e-54</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -587,40 +599,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1740</v>
+        <v>1680</v>
       </c>
       <c r="C4" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="D4" t="n">
-        <v>13.13035016063563</v>
+        <v>13.11091558692563</v>
       </c>
       <c r="E4" t="n">
-        <v>13.92767637135523</v>
+        <v>13.92678283199101</v>
       </c>
       <c r="F4" t="n">
-        <v>4.511292679129842</v>
+        <v>4.423708757956064</v>
       </c>
       <c r="G4" t="n">
-        <v>2.638220292100501</v>
+        <v>2.727179900905868</v>
       </c>
       <c r="H4" t="n">
-        <v>13.42110858010625</v>
+        <v>13.412492890532</v>
       </c>
       <c r="I4" t="n">
         <v>13.7114491810391</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2903406009328506</v>
+        <v>0.2989562905070997</v>
       </c>
       <c r="K4" t="n">
-        <v>329371.5</v>
+        <v>363216.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001686375294977178</v>
+        <v>0.0009069678876473791</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00674550117990871</v>
+        <v>0.003627871550589516</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -633,40 +645,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1740</v>
+        <v>1680</v>
       </c>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="D5" t="n">
-        <v>89.6480601292898</v>
+        <v>89.51578887159145</v>
       </c>
       <c r="E5" t="n">
-        <v>76.84079136845779</v>
+        <v>77.0916950891592</v>
       </c>
       <c r="F5" t="n">
-        <v>21.98298173357575</v>
+        <v>21.8259299675743</v>
       </c>
       <c r="G5" t="n">
-        <v>30.77366389370666</v>
+        <v>30.80530331724373</v>
       </c>
       <c r="H5" t="n">
-        <v>91.22946787432775</v>
+        <v>91.1431333144636</v>
       </c>
       <c r="I5" t="n">
-        <v>79.12427681856781</v>
+        <v>79.98939145202375</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.10519105575995</v>
+        <v>-11.15374186243984</v>
       </c>
       <c r="K5" t="n">
-        <v>450198</v>
+        <v>493105</v>
       </c>
       <c r="L5" t="n">
-        <v>1.449134533062786e-13</v>
+        <v>8.617817577443077e-14</v>
       </c>
       <c r="M5" t="n">
-        <v>5.796538132251142e-13</v>
+        <v>3.447127030977231e-13</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
